--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim-10.xlsx
@@ -52,7 +52,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Classification internationale des maladies 10eme révision, version française à usage PMSI (Programme Médicalisé des Systèmes d'Information)</t>
+    <t>Classification internationale des maladies et des problèmes de santé connexes - 10ème révision - Version française à usage PMSI (Programme Médicalisé des Systèmes d'Information)</t>
   </si>
   <si>
     <t>Status</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim-10.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim-10.xlsx
@@ -118,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>19161</t>
+    <t>19075</t>
   </si>
   <si>
     <t>Code</t>
